--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104520_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104520_W7.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1861</v>
+        <v>1.3678</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6373</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4512</v>
+        <v>0.4086</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.008200000000000001</v>
+        <v>3.0424</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1357</v>
+        <v>0.1854</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1439</v>
+        <v>2.8569</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1048</v>
+        <v>3.0966</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9555</v>
+        <v>0.4309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>2.6657</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.113</v>
+        <v>-0.0543</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8198</v>
+        <v>-0.2455</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2931</v>
+        <v>0.1912</v>
       </c>
       <c r="P2" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1.5934</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.8211</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-1.7617</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.544</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.2177</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.1405</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-2.2683</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.2683</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.9409</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.4548</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.5139</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.2534</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.3461</v>
-      </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2517</v>
+        <v>1.2819</v>
       </c>
       <c r="E3" t="n">
-        <v>1.439</v>
+        <v>1.7316</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1873</v>
+        <v>-0.4497</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3692</v>
+        <v>-0.0013</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5585</v>
+        <v>0.1323</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1893</v>
+        <v>-0.1336</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7818</v>
+        <v>1.0862</v>
       </c>
       <c r="K3" t="n">
-        <v>1.638</v>
+        <v>0.9373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1439</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4126</v>
+        <v>-1.0876</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0795</v>
+        <v>-0.805</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3331</v>
+        <v>-0.2826</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3342</v>
+        <v>0.0359</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0162</v>
+        <v>0.5849</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.549</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2249</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2249</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1081</v>
+        <v>1.113</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1899</v>
+        <v>2.2407</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0818</v>
+        <v>-1.1277</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4195</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1442</v>
+        <v>-0.1491</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5637</v>
+        <v>3.5491</v>
       </c>
       <c r="J4" t="n">
-        <v>4.361</v>
+        <v>4.3017</v>
       </c>
       <c r="K4" t="n">
-        <v>0.976</v>
+        <v>0.9438</v>
       </c>
       <c r="L4" t="n">
-        <v>3.385</v>
+        <v>3.3579</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9415</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1202</v>
+        <v>-1.0929</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6917</v>
+        <v>-0.6701</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3902</v>
+        <v>0.5128</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0819</v>
+        <v>-1.1829</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6197</v>
+        <v>-1.6169</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7804</v>
+        <v>-1.7747</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5988</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9849</v>
+        <v>0.735</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4108</v>
+        <v>-0.1362</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0541</v>
+        <v>-1.8862</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6379</v>
+        <v>-1.3277</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5838</v>
+        <v>-0.5586</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1985</v>
+        <v>-0.1381</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0866</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2526</v>
+        <v>-1.7481</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7245</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4718</v>
+        <v>-1.0722</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7126</v>
+        <v>0.0011</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7864</v>
+        <v>0.2876</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0738</v>
+        <v>-0.2865</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7649</v>
+        <v>2.2563</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7649</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5516</v>
+        <v>0.5162</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2744</v>
+        <v>0.5336</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2773</v>
+        <v>-0.0174</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0228</v>
+        <v>1.3575</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1627</v>
+        <v>1.5513</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8601</v>
+        <v>-0.1939</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1143</v>
+        <v>1.7571</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4329</v>
+        <v>1.6235</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6814</v>
+        <v>0.1336</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0915</v>
+        <v>-0.3997</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2702</v>
+        <v>-0.0722</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1787</v>
+        <v>-0.3275</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.5566</v>
+        <v>-0.3845</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2521</v>
+        <v>0.1438</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3045</v>
+        <v>-0.5283</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1414</v>
+        <v>-0.2292</v>
       </c>
       <c r="W6" t="n">
+        <v>-0.2292</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.1414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3911</v>
+        <v>0.3591</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2124</v>
+        <v>0.6322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1787</v>
+        <v>-0.2731</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9019</v>
+        <v>-0.0467</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3422</v>
+        <v>-0.6322</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5598</v>
+        <v>0.5855</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1281</v>
+        <v>0.1979</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6478</v>
+        <v>0.0862</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.1117</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7738</v>
+        <v>-0.2446</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-0.7184</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0795</v>
+        <v>0.4738</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1963</v>
+        <v>0.4855</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2571</v>
+        <v>0.4343</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0608</v>
+        <v>0.0512</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2625</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0771</v>
+        <v>-0.7625999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7155</v>
+        <v>-1.2139</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-1.1191</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6203</v>
+        <v>-0.0948</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2043</v>
+        <v>0.6862</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.215</v>
+        <v>0.2958</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0107</v>
+        <v>0.3903</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0.9018</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7415</v>
+        <v>0.8274</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1866</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6494</v>
+        <v>-0.2157</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4735</v>
+        <v>-0.5315</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1759</v>
+        <v>0.3159</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4888</v>
+        <v>0.5168</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5939</v>
+        <v>0.483</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1051</v>
+        <v>0.0338</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.88</v>
+        <v>-1.7422</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-1.3327</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0075</v>
+        <v>-0.4095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6850000000000001</v>
+        <v>-1.2984</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2958</v>
+        <v>-0.5716</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3892</v>
+        <v>-0.7268</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9058</v>
+        <v>-0.3672</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8312</v>
+        <v>0.348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2209</v>
+        <v>-0.9312</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5354</v>
+        <v>-0.9196</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3145</v>
+        <v>-0.0116</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8447</v>
+        <v>-1.374</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7168</v>
+        <v>-0.5298</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1279</v>
+        <v>-0.8441</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1414</v>
+        <v>0.7025</v>
       </c>
       <c r="W9" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.1414</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8806</v>
+        <v>-1.9993</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5475</v>
+        <v>-1.5231</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3332</v>
+        <v>-0.4763</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3032</v>
+        <v>-1.1955</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5729</v>
+        <v>-1.2122</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7302999999999999</v>
+        <v>0.0166</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3552</v>
+        <v>-0.5657</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3565</v>
+        <v>-0.7519</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7117</v>
+        <v>0.1862</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.948</v>
+        <v>-0.6298</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9294</v>
+        <v>-0.4603</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0186</v>
+        <v>-0.1695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5113</v>
+        <v>-0.8038</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7652</v>
+        <v>0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7461</v>
+        <v>-0.9846</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0829</v>
+        <v>-2.5895</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6069</v>
+        <v>-2.3771</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.476</v>
+        <v>-0.2125</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5017</v>
+        <v>-1.5229</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.1325</v>
+        <v>-4.1411</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6308</v>
+        <v>2.6182</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1434</v>
+        <v>0.0814</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6819</v>
+        <v>-2.7179</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8252</v>
+        <v>2.7993</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6451</v>
+        <v>-1.6043</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4506</v>
+        <v>-1.4232</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R11" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.8027</v>
+        <v>-1.2904</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3912</v>
+        <v>-0.0912</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4115</v>
+        <v>-1.1992</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9126</v>
+        <v>-0.9144</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1414</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0401</v>
+        <v>-5.8465</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.335</v>
+        <v>-4.0491</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7051</v>
+        <v>-1.7974</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7434</v>
+        <v>-2.729</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3273</v>
+        <v>0.341</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0707</v>
+        <v>-3.0701</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0913</v>
+        <v>-2.1021</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6521</v>
+        <v>-0.627</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2721</v>
+        <v>-1.0962</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0434</v>
+        <v>-0.7389</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2287</v>
+        <v>-0.3573</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2706</v>
+        <v>-6.3093</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5904</v>
+        <v>-3.7099</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6802</v>
+        <v>-2.5993</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.4132</v>
+        <v>-5.4181</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6552</v>
+        <v>-0.6494</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.7581</v>
+        <v>-4.7687</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.8252</v>
+        <v>-3.842</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.8945</v>
+        <v>-3.911</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.588</v>
+        <v>-1.5761</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3525</v>
+        <v>-0.3951</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>0.1321</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5873</v>
+        <v>-0.5272</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.807</v>
+        <v>-14.4639</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.3096</v>
+        <v>-7.278700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.497400000000001</v>
+        <v>-7.1853</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.633499999999999</v>
+        <v>-5.612</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.2199</v>
+        <v>-6.177499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5861999999999989</v>
+        <v>0.5649000000000006</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6549</v>
+        <v>4.407600000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>1.430699999999999</v>
+        <v>1.2996</v>
       </c>
       <c r="L14" t="n">
-        <v>3.224400000000002</v>
+        <v>3.107999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.2885</v>
+        <v>-10.0201</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.650499999999999</v>
+        <v>-7.476999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.6382</v>
+        <v>-2.5431</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R14" t="n">
-        <v>18.1467</v>
+        <v>18.2107</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.062</v>
+        <v>-6.7365</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4841000000000003</v>
+        <v>0.8553999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.5461</v>
+        <v>-7.591800000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.245499999999999</v>
+        <v>-3.2535</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5638</v>
+        <v>4.5306</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.8094</v>
+        <v>-7.784</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6347</v>
+        <v>8.519</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5144</v>
+        <v>5.4233</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1203</v>
+        <v>3.0957</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5922</v>
+        <v>5.5891</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5064</v>
+        <v>0.5083</v>
       </c>
       <c r="I15" t="n">
-        <v>5.0858</v>
+        <v>5.0809</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6689</v>
+        <v>4.6396</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9799</v>
+        <v>0.9685</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6889</v>
+        <v>3.6711</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9233</v>
+        <v>0.9495</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3412</v>
+        <v>0.5413</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6593</v>
+        <v>0.2876</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3181</v>
+        <v>0.2537</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5948</v>
+        <v>8.1669</v>
       </c>
       <c r="E16" t="n">
-        <v>6.3337</v>
+        <v>6.8682</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2611</v>
+        <v>1.2987</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1906</v>
+        <v>3.1737</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0608</v>
+        <v>1.0435</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1298</v>
+        <v>2.1302</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4054</v>
+        <v>3.3529</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2762</v>
+        <v>0.2403</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2148</v>
+        <v>-0.1792</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7847</v>
+        <v>0.8032</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9994</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1422</v>
+        <v>0.4484</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1966</v>
+        <v>0.7916</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3388</v>
+        <v>-0.3432</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.968</v>
+        <v>2.7141</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7002</v>
+        <v>0.6401</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7322</v>
+        <v>2.074</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0809</v>
+        <v>4.0483</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1283</v>
+        <v>2.6629</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0475</v>
+        <v>1.3854</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9674</v>
+        <v>2.5123</v>
       </c>
       <c r="K17" t="n">
-        <v>4.485</v>
+        <v>2.7062</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4824</v>
+        <v>-0.1939</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8866000000000001</v>
+        <v>1.536</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6433</v>
+        <v>-0.0433</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5299</v>
+        <v>1.5793</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4601</v>
+        <v>0.2592</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9084</v>
+        <v>0.4041</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5516</v>
+        <v>-0.1449</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2855</v>
+        <v>2.6455</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1916</v>
+        <v>5.0797</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0939</v>
+        <v>-2.4343</v>
       </c>
       <c r="G18" t="n">
-        <v>4.0545</v>
+        <v>4.0878</v>
       </c>
       <c r="H18" t="n">
-        <v>2.671</v>
+        <v>5.124</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3834</v>
+        <v>-1.0363</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5294</v>
+        <v>4.9408</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7187</v>
+        <v>4.4643</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1893</v>
+        <v>0.4764</v>
       </c>
       <c r="M18" t="n">
-        <v>1.525</v>
+        <v>-0.853</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0477</v>
+        <v>0.6597</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5727</v>
+        <v>-1.5127</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1812</v>
+        <v>1.1221</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>1.3258</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1116</v>
+        <v>-0.2037</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1313</v>
+        <v>0.7869</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2201</v>
+        <v>-0.7461</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9113</v>
+        <v>1.533</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8426</v>
+        <v>-2.8425</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4992</v>
+        <v>-1.5019</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3434</v>
+        <v>-1.3405</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4896</v>
+        <v>-1.51</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.353</v>
+        <v>-1.3325</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9739</v>
+        <v>1.6294</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7512</v>
+        <v>0.8126</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2228</v>
+        <v>0.8168</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4766</v>
+        <v>-0.7407</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1432</v>
+        <v>-2.8341</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6667</v>
+        <v>2.0934</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1075</v>
+        <v>-0.496</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9076</v>
+        <v>-0.7463</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1999</v>
+        <v>0.2504</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0998</v>
+        <v>-0.841</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1744</v>
+        <v>-0.2003</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-0.6407</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0077</v>
+        <v>0.3451</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2669</v>
+        <v>-0.546</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2745</v>
+        <v>0.8911</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9938</v>
+        <v>0.7341</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2249</v>
+        <v>0.2832</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2311</v>
+        <v>0.4509</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7712</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7712</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4789</v>
+        <v>-1.0882</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1913</v>
+        <v>-0.9035</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6702</v>
+        <v>-0.1847</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7607</v>
+        <v>-3.7561</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.567</v>
+        <v>-1.5681</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1937</v>
+        <v>-2.188</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.096</v>
+        <v>-3.1295</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9982</v>
+        <v>-1.0212</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0979</v>
+        <v>-2.1083</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6647</v>
+        <v>-0.6266</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5689</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>1.762</v>
+        <v>1.1428</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7825</v>
+        <v>1.7299</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0205</v>
+        <v>-0.5871</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.206</v>
+        <v>-1.1761</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2833</v>
+        <v>-2.983</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0773</v>
+        <v>1.8069</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4908</v>
+        <v>-1.1068</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7387</v>
+        <v>-0.9103</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2479</v>
+        <v>-0.1965</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8245</v>
+        <v>-1.1084</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1874</v>
+        <v>-1.1828</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6371</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3337</v>
+        <v>0.0016</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5513</v>
+        <v>0.2725</v>
       </c>
       <c r="O22" t="n">
-        <v>0.885</v>
+        <v>-0.271</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2601</v>
+        <v>0.2949</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1905</v>
+        <v>0.4016</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4506</v>
+        <v>-0.1067</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>0.7739</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3856</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0784</v>
+        <v>-1.9673</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6822</v>
+        <v>-1.0263</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3962</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3923</v>
+        <v>0.3894</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6451</v>
+        <v>1.6375</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2528</v>
+        <v>-1.2481</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8484</v>
+        <v>2.8069</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8835</v>
+        <v>1.8541</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.456</v>
+        <v>-2.4175</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2384</v>
+        <v>-0.2166</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2176</v>
+        <v>-2.2009</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5634</v>
+        <v>0.5538</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0061</v>
+        <v>0.7195</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5695</v>
+        <v>-0.1656</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5674</v>
+        <v>-3.0476</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.545</v>
+        <v>-2.3329</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0223</v>
+        <v>-0.7147</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4754</v>
+        <v>-3.4748</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.3959</v>
+        <v>-3.4026</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6211</v>
+        <v>-1.6437</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2669</v>
+        <v>-0.2725</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3542</v>
+        <v>-1.3712</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8543</v>
+        <v>-1.831</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.16</v>
+        <v>0.3589</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5958</v>
+        <v>0.8359</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7558</v>
+        <v>-0.4771</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.807</v>
+        <v>14.8125</v>
       </c>
       <c r="E25" t="n">
-        <v>7.497599999999998</v>
+        <v>7.1854</v>
       </c>
       <c r="F25" t="n">
-        <v>7.309700000000001</v>
+        <v>7.627</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6335</v>
+        <v>5.612099999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>6.2196</v>
+        <v>6.1774</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5862999999999996</v>
+        <v>-0.5651000000000006</v>
       </c>
       <c r="J25" t="n">
-        <v>10.2885</v>
+        <v>10.0199</v>
       </c>
       <c r="K25" t="n">
-        <v>7.650200000000002</v>
+        <v>7.476900000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>2.637999999999999</v>
+        <v>2.543</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.6551</v>
+        <v>-4.4076</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4305</v>
+        <v>-1.2997</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.2244</v>
+        <v>-3.1082</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q25" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R25" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S25" t="n">
-        <v>7.0619</v>
+        <v>7.0849</v>
       </c>
       <c r="T25" t="n">
-        <v>7.5461</v>
+        <v>7.5918</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4841999999999999</v>
+        <v>-0.5069</v>
       </c>
       <c r="V25" t="n">
-        <v>3.2456</v>
+        <v>3.2536</v>
       </c>
       <c r="W25" t="n">
-        <v>7.8095</v>
+        <v>7.784099999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.5638</v>
+        <v>-4.5306</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104520_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104520_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.7747</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7625999999999999</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.784</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104520_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.5306</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
